--- a/.cloud_chaos_data/game_sessions_backup.xlsx
+++ b/.cloud_chaos_data/game_sessions_backup.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>session_id</t>
   </si>
@@ -44,18 +44,6 @@
   </si>
   <si>
     <t>completed_at</t>
-  </si>
-  <si>
-    <t>Shahid Nazeer Syed</t>
-  </si>
-  <si>
-    <t>Graphic Designer</t>
-  </si>
-  <si>
-    <t>shahidnazeerwork2@gmail.com</t>
-  </si>
-  <si>
-    <t>2026-03-16 09:46:45.839038</t>
   </si>
 </sst>
 </file>
@@ -413,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -448,38 +436,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>50</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/.cloud_chaos_data/game_sessions_backup.xlsx
+++ b/.cloud_chaos_data/game_sessions_backup.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>session_id</t>
   </si>
@@ -44,6 +44,18 @@
   </si>
   <si>
     <t>completed_at</t>
+  </si>
+  <si>
+    <t>Shahid Nazeer Syed</t>
+  </si>
+  <si>
+    <t>Graphic Designer</t>
+  </si>
+  <si>
+    <t>shahidnazeerwork2@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-16 09:46:45.839038</t>
   </si>
 </sst>
 </file>
@@ -401,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -436,6 +448,38 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2" spans="1:10">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>50</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
